--- a/inventory/files/2026-W42/STA_EU_AUTO_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_EU_AUTO_2026-W42.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4664</v>
+        <v>4786</v>
       </c>
     </row>
     <row r="10">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>651</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="13">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>302</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
